--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post DFS_HRM-2031-0272/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post DFS_HRM-2031-0272/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.55215</v>
+        <v>16.76605</v>
       </c>
       <c r="D2" t="n">
-        <v>16.46978</v>
+        <v>16.64018</v>
       </c>
       <c r="E2" t="n">
-        <v>16.72826</v>
+        <v>16.70928</v>
       </c>
       <c r="F2" t="n">
-        <v>42.25398</v>
+        <v>42.75284</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05169</v>
+        <v>0.04918</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81693</v>
+        <v>1.80646</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.82627</v>
+        <v>17.13932</v>
       </c>
       <c r="D3" t="n">
-        <v>16.66121</v>
+        <v>16.52438</v>
       </c>
       <c r="E3" t="n">
-        <v>16.43614</v>
+        <v>16.87969</v>
       </c>
       <c r="F3" t="n">
-        <v>41.66479</v>
+        <v>43.24872</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05066</v>
+        <v>0.05033</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80006</v>
+        <v>1.79703</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.94392</v>
+        <v>17.10781</v>
       </c>
       <c r="D4" t="n">
-        <v>16.7651</v>
+        <v>16.51811</v>
       </c>
       <c r="E4" t="n">
-        <v>16.78019</v>
+        <v>16.62916</v>
       </c>
       <c r="F4" t="n">
-        <v>42.76477</v>
+        <v>41.27977</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05108</v>
+        <v>0.04995</v>
       </c>
       <c r="H4" t="n">
-        <v>1.79299</v>
+        <v>1.84809</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.50074</v>
+        <v>16.68236</v>
       </c>
       <c r="D6" t="n">
-        <v>15.67244</v>
+        <v>15.91537</v>
       </c>
       <c r="E6" t="n">
-        <v>16.32273</v>
+        <v>16.39582</v>
       </c>
       <c r="F6" t="n">
-        <v>22.07029</v>
+        <v>21.6439</v>
       </c>
       <c r="G6" t="n">
-        <v>34.31874</v>
+        <v>34.15703</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.73786</v>
+        <v>16.79999</v>
       </c>
       <c r="D7" t="n">
-        <v>15.90466</v>
+        <v>15.91437</v>
       </c>
       <c r="E7" t="n">
-        <v>16.663</v>
+        <v>16.11102</v>
       </c>
       <c r="F7" t="n">
-        <v>21.90997</v>
+        <v>21.7636</v>
       </c>
       <c r="G7" t="n">
-        <v>34.40925</v>
+        <v>34.33284</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.82128</v>
+        <v>16.76929</v>
       </c>
       <c r="D8" t="n">
-        <v>15.87586</v>
+        <v>15.78364</v>
       </c>
       <c r="E8" t="n">
-        <v>16.21711</v>
+        <v>16.39716</v>
       </c>
       <c r="F8" t="n">
-        <v>21.93422</v>
+        <v>21.23833</v>
       </c>
       <c r="G8" t="n">
-        <v>33.76329</v>
+        <v>33.94942</v>
       </c>
     </row>
   </sheetData>
